--- a/MainTop/23.04.2026 Таня ВБ/print_print_sorted.xlsx
+++ b/MainTop/23.04.2026 Таня ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\23.04.2026 Таня ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD5E02B-8445-4C96-BEE1-FBEFC8B3874B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935BC2D0-F6B6-47D3-BB45-2210F22CC345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -859,10 +859,10 @@
   <dimension ref="A1:E136"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.28515625" customWidth="1"/>
+    <col min="1" max="1" width="43.7109375" customWidth="1"/>
     <col min="2" max="2" width="6.5703125" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3313,6 +3313,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>Страница &amp;P</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/MainTop/23.04.2026 Таня ВБ/print_print_sorted.xlsx
+++ b/MainTop/23.04.2026 Таня ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\23.04.2026 Таня ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935BC2D0-F6B6-47D3-BB45-2210F22CC345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F82E7A-A9E5-4F97-BCE6-F6DFBA2CD540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2894,8 +2894,7 @@
         <v>6</v>
       </c>
       <c r="E113" s="2">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">

--- a/MainTop/23.04.2026 Таня ВБ/print_print_sorted.xlsx
+++ b/MainTop/23.04.2026 Таня ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\23.04.2026 Таня ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F82E7A-A9E5-4F97-BCE6-F6DFBA2CD540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CCE481-2370-4D71-8F28-85A56405171E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -472,7 +472,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -481,37 +481,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
+        <fgColor theme="8"/>
         <bgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99CCFF"/>
+        <fgColor theme="8"/>
         <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor theme="8"/>
         <bgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFCC"/>
+        <fgColor theme="8"/>
         <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCCCFF"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFA07A"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF99CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor rgb="FFFFA07A"/>
       </patternFill>
     </fill>
@@ -543,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -554,6 +572,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1369,1944 +1390,1944 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="6">
         <v>20</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" s="2">
+      <c r="C29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="6">
         <v>20</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30" s="2">
+      <c r="C30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="6">
         <v>20</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="2">
+      <c r="C31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="6">
         <v>20</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32" s="2">
+      <c r="C32" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="6">
         <v>20</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="2">
+      <c r="C33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="6">
         <v>16</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E34" s="2">
+      <c r="C34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="6">
         <v>16</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" s="2">
+      <c r="C35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="6">
         <v>16</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" s="2">
+      <c r="C36" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="6">
         <v>16</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" s="2">
+      <c r="C37" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="6">
         <v>16</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="2">
+      <c r="C38" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="6">
         <v>16</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="2">
+      <c r="C39" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="6">
         <v>16</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" s="2">
+      <c r="C40" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="6">
         <v>16</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41" s="2">
+      <c r="C41" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="6">
         <v>16</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42" s="2">
+      <c r="C42" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="6">
         <v>12</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" s="2">
+      <c r="C43" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="6">
         <v>12</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" s="2">
+      <c r="C44" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="6">
         <v>12</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" s="2">
+      <c r="C45" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="6">
         <v>12</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E46" s="2">
+      <c r="C46" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="6">
         <v>12</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E47" s="2">
+      <c r="C47" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48" s="8">
         <v>12</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E48" s="2">
+      <c r="C48" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="8">
         <v>12</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49" s="2">
+      <c r="C49" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="6">
+      <c r="B50" s="8">
         <v>12</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50" s="2">
+      <c r="C50" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="8">
         <v>8</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="2">
+      <c r="C51" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="6">
+      <c r="B52" s="8">
         <v>8</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52" s="2">
+      <c r="C52" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="8">
         <v>8</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" s="2">
+      <c r="C53" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B54" s="8">
         <v>8</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54" s="2">
+      <c r="C54" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="8">
         <v>8</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" s="2">
+      <c r="C55" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E55" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B56" s="8">
         <v>8</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E56" s="2">
+      <c r="C56" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="8">
         <v>8</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57" s="2">
+      <c r="C57" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58" s="8">
         <v>8</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58" s="2">
+      <c r="C58" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="8">
         <v>8</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59" s="2">
+      <c r="C59" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="6">
+      <c r="B60" s="8">
         <v>8</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E60" s="2">
+      <c r="C60" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="8">
         <v>8</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61" s="2">
+      <c r="C61" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E61" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B62" s="8">
         <v>8</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E62" s="2">
+      <c r="C62" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E62" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63" s="8">
         <v>8</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E63" s="2">
+      <c r="C63" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E63" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="6">
+      <c r="B64" s="8">
         <v>8</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E64" s="2">
+      <c r="C64" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E64" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="8">
         <v>8</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E65" s="2">
+      <c r="C65" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E65" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B66" s="8">
         <v>8</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E66" s="2">
+      <c r="C66" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B67" s="6">
-        <v>4</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E67" s="2">
+      <c r="B67" s="8">
+        <v>4</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E67" s="7">
         <f t="shared" ref="E67:E130" si="1">B67/4</f>
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B68" s="6">
-        <v>4</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E68" s="2">
+      <c r="B68" s="8">
+        <v>4</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E68" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="6">
-        <v>4</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E69" s="2">
+      <c r="B69" s="8">
+        <v>4</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E69" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B70" s="6">
-        <v>4</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E70" s="2">
+      <c r="B70" s="8">
+        <v>4</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E70" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B71" s="6">
-        <v>4</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E71" s="2">
+      <c r="B71" s="8">
+        <v>4</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E71" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B72" s="6">
-        <v>4</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E72" s="2">
+      <c r="B72" s="8">
+        <v>4</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E72" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B73" s="6">
-        <v>4</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E73" s="2">
+      <c r="B73" s="8">
+        <v>4</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E73" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="6">
-        <v>4</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E74" s="2">
+      <c r="B74" s="8">
+        <v>4</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E74" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B75" s="6">
-        <v>4</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E75" s="2">
+      <c r="B75" s="8">
+        <v>4</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E75" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="6">
-        <v>4</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E76" s="2">
+      <c r="B76" s="8">
+        <v>4</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E76" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B77" s="6">
-        <v>4</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E77" s="2">
+      <c r="B77" s="8">
+        <v>4</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E77" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="6">
-        <v>4</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E78" s="2">
+      <c r="B78" s="8">
+        <v>4</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E78" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="6">
-        <v>4</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E79" s="2">
+      <c r="B79" s="8">
+        <v>4</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E79" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="6">
-        <v>4</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E80" s="2">
+      <c r="B80" s="8">
+        <v>4</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E80" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="6">
-        <v>4</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E81" s="2">
+      <c r="B81" s="8">
+        <v>4</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E81" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B82" s="6">
-        <v>4</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E82" s="2">
+      <c r="B82" s="8">
+        <v>4</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E82" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B83" s="6">
-        <v>4</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E83" s="2">
+      <c r="B83" s="8">
+        <v>4</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E83" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B84" s="6">
-        <v>4</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E84" s="2">
+      <c r="B84" s="8">
+        <v>4</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E84" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B85" s="6">
-        <v>4</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E85" s="2">
+      <c r="B85" s="8">
+        <v>4</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E85" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B86" s="6">
-        <v>4</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E86" s="2">
+      <c r="B86" s="8">
+        <v>4</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E86" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B87" s="6">
-        <v>4</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E87" s="2">
+      <c r="B87" s="8">
+        <v>4</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E87" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B88" s="6">
-        <v>4</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E88" s="2">
+      <c r="B88" s="8">
+        <v>4</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E88" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B89" s="6">
-        <v>4</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E89" s="2">
+      <c r="B89" s="8">
+        <v>4</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E89" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B90" s="6">
-        <v>4</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E90" s="2">
+      <c r="B90" s="8">
+        <v>4</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E90" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B91" s="6">
-        <v>4</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E91" s="2">
+      <c r="B91" s="8">
+        <v>4</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E91" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B92" s="6">
-        <v>4</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E92" s="2">
+      <c r="B92" s="8">
+        <v>4</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E92" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B93" s="6">
-        <v>4</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E93" s="2">
+      <c r="B93" s="8">
+        <v>4</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E93" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B94" s="6">
-        <v>4</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E94" s="2">
+      <c r="B94" s="8">
+        <v>4</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E94" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B95" s="6">
-        <v>4</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E95" s="2">
+      <c r="B95" s="8">
+        <v>4</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E95" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B96" s="6">
-        <v>4</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E96" s="2">
+      <c r="B96" s="8">
+        <v>4</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E96" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B97" s="6">
-        <v>4</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E97" s="2">
+      <c r="B97" s="8">
+        <v>4</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E97" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B98" s="6">
-        <v>4</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E98" s="2">
+      <c r="B98" s="8">
+        <v>4</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E98" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B99" s="6">
-        <v>4</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E99" s="2">
+      <c r="B99" s="8">
+        <v>4</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E99" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B100" s="6">
+      <c r="B100" s="8">
         <v>52</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E100" s="2">
+      <c r="C100" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E100" s="7">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="7">
         <v>44</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E101" s="2">
+      <c r="C101" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E101" s="7">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B102" s="7">
         <v>36</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E102" s="2">
+      <c r="C102" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E102" s="7">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="7">
         <v>32</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E103" s="2">
+      <c r="C103" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E103" s="7">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104" s="7">
         <v>28</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E104" s="2">
+      <c r="C104" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E104" s="7">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="7">
         <v>28</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E105" s="2">
+      <c r="C105" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E105" s="7">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="7">
         <v>20</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E106" s="2">
+      <c r="C106" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E106" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="7">
         <v>16</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E107" s="2">
+      <c r="C107" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E107" s="7">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108" s="7">
         <v>16</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E108" s="2">
+      <c r="C108" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E108" s="7">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="7">
         <v>12</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E109" s="2">
+      <c r="C109" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E109" s="7">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110" s="7">
         <v>12</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E110" s="2">
+      <c r="C110" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E110" s="7">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="7">
         <v>12</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E111" s="2">
+      <c r="C111" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E111" s="7">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112" s="7">
         <v>12</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E112" s="2">
+      <c r="C112" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E112" s="7">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="7">
         <v>12</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E113" s="2">
+      <c r="C113" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E113" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B114" s="2">
+      <c r="B114" s="7">
         <v>12</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E114" s="2">
+      <c r="C114" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E114" s="7">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" s="7">
         <v>8</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E115" s="2">
+      <c r="C115" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E115" s="7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116" s="7">
         <v>8</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E116" s="2">
+      <c r="C116" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E116" s="7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="7">
         <v>8</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E117" s="2">
+      <c r="C117" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E117" s="7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="7">
         <v>8</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E118" s="2">
+      <c r="C118" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E118" s="7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="7">
         <v>8</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E119" s="2">
+      <c r="C119" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E119" s="7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="7">
         <v>8</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E120" s="2">
+      <c r="C120" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E120" s="7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="7">
         <v>8</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E121" s="2">
+      <c r="C121" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E121" s="7">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
+      <c r="A122" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B122" s="3">
-        <v>4</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E122" s="2">
+      <c r="B122" s="9">
+        <v>4</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E122" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B123" s="3">
-        <v>4</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E123" s="2">
+      <c r="B123" s="9">
+        <v>4</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E123" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
+      <c r="A124" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B124" s="3">
-        <v>4</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E124" s="2">
+      <c r="B124" s="9">
+        <v>4</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E124" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
+      <c r="A125" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B125" s="3">
-        <v>4</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E125" s="2">
+      <c r="B125" s="9">
+        <v>4</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E125" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
+      <c r="A126" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B126" s="3">
-        <v>4</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E126" s="2">
+      <c r="B126" s="9">
+        <v>4</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E126" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B127" s="3">
-        <v>4</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E127" s="2">
+      <c r="B127" s="9">
+        <v>4</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E127" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="s">
+      <c r="A128" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B128" s="3">
-        <v>4</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E128" s="2">
+      <c r="B128" s="9">
+        <v>4</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E128" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
+      <c r="A129" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B129" s="3">
-        <v>4</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E129" s="2">
+      <c r="B129" s="9">
+        <v>4</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E129" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
+      <c r="A130" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B130" s="3">
-        <v>4</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E130" s="2">
+      <c r="B130" s="9">
+        <v>4</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E130" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
+      <c r="A131" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B131" s="3">
-        <v>4</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E131" s="2">
+      <c r="B131" s="9">
+        <v>4</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E131" s="7">
         <f t="shared" ref="E131:E136" si="2">B131/4</f>
         <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="s">
+      <c r="A132" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B132" s="3">
-        <v>4</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E132" s="2">
+      <c r="B132" s="9">
+        <v>4</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E132" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
+      <c r="A133" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B133" s="3">
-        <v>4</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E133" s="2">
+      <c r="B133" s="9">
+        <v>4</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E133" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
+      <c r="A134" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B134" s="3">
-        <v>4</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E134" s="2">
+      <c r="B134" s="9">
+        <v>4</v>
+      </c>
+      <c r="C134" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E134" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
+      <c r="A135" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B135" s="7">
-        <v>4</v>
-      </c>
-      <c r="C135" s="7" t="s">
+      <c r="B135" s="10">
+        <v>4</v>
+      </c>
+      <c r="C135" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D135" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E135" s="2">
+      <c r="D135" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E135" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="7" t="s">
+      <c r="A136" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B136" s="7">
-        <v>4</v>
-      </c>
-      <c r="C136" s="7" t="s">
+      <c r="B136" s="10">
+        <v>4</v>
+      </c>
+      <c r="C136" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D136" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E136" s="2">
+      <c r="D136" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E136" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
